--- a/api_test_report.xlsx
+++ b/api_test_report.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -505,21 +505,21 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/api-keys</t>
+          <t>/actuator/health</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Mint admin API key (X-Admin-Key gated)</t>
+          <t>Health check</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -544,11 +544,11 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>List API keys (X-Admin-Key gated)</t>
+          <t>Mint admin key with X-Admin-Key</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -563,21 +563,21 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/api-keys/{id}</t>
+          <t>/api/v1/api-keys</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Revoke API key (X-Admin-Key gated)</t>
+          <t>List keys with X-Admin-Key</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -592,32 +592,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/api-keys</t>
+          <t>/api/v1/api-keys/{id}</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Missing X-Admin-Key</t>
+          <t>Revoke key with X-Admin-Key</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>401</v>
+        <v>204</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Expected 401 rejection</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -635,7 +631,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Wrong X-Admin-Key</t>
+          <t>Missing X-Admin-Key</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -648,7 +644,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Expected 401 rejection</t>
+          <t>Expected 401 rejection of missing admin key</t>
         </is>
       </c>
     </row>
@@ -663,16 +659,16 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/spaces</t>
+          <t>/api/v1/api-keys</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>No X-API-Key header</t>
+          <t>Wrong X-Admin-Key</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -681,7 +677,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Expected 401/403 rejection</t>
+          <t>Expected 401 rejection of invalid admin key</t>
         </is>
       </c>
     </row>
@@ -701,18 +697,22 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>List spaces with valid key</t>
+          <t>No X-API-Key</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Expected 403 rejection of unauthenticated request</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -720,7 +720,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -730,11 +730,11 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Create space (Admin)</t>
+          <t>List spaces (includes averageRating/totalReviews)</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -749,21 +749,21 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/spaces/{id}</t>
+          <t>/api/v1/spaces</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Get single space</t>
+          <t>Create space (Admin)</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -783,12 +783,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/spaces?type=DESK</t>
+          <t>/api/v1/spaces/{id}</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Filter spaces by type</t>
+          <t>Get single space (includes averageRating/totalReviews)</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -807,17 +807,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/spaces/{id}</t>
+          <t>/api/v1/spaces?type=DESK</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Update space</t>
+          <t>Filter by type</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -846,11 +846,11 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Soft delete space</t>
+          <t>Update space</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -875,22 +875,18 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Get space after delete</t>
+          <t>Soft delete space</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>404</v>
+        <v>204</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Expected 404 after soft delete</t>
-        </is>
-      </c>
+      <c r="G14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -898,21 +894,21 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/spaces</t>
+          <t>/api/v1/spaces/{id}</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Create space missing required fields</t>
+          <t>Get after delete</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -921,7 +917,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Expected 400 validation error</t>
+          <t>Expected 404 for deleted resource</t>
         </is>
       </c>
     </row>
@@ -931,28 +927,32 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/membership-plans</t>
+          <t>/api/v1/spaces</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>List membership plans</t>
+          <t>Missing required fields</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Expected 400 validation failure</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Create membership plan (Admin)</t>
+          <t>List plans</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/membership-plans/{id}</t>
+          <t>/api/v1/membership-plans</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Get single membership plan</t>
+          <t>Create plan (Admin)</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1028,11 +1028,11 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Delete membership plan</t>
+          <t>Get single plan</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1057,22 +1057,18 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Get plan after delete</t>
+          <t>Delete plan</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>404</v>
+        <v>204</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Expected 404 after delete</t>
-        </is>
-      </c>
+      <c r="G20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1085,23 +1081,27 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/membership-plans/{id}</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>List users (Admin)</t>
+          <t>Get after delete</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>200</v>
+        <v>404</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Expected 404 for deleted resource</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1119,11 +1119,11 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Create user (auto-mints linked API key)</t>
+          <t>List users (Admin)</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users/{id}</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Get single user</t>
+          <t>Create user + auto-mint linked API key</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Update user</t>
+          <t>Get single user</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Soft delete user</t>
+          <t>Update user</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1235,22 +1235,18 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Get user after delete</t>
+          <t>Soft delete user</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>404</v>
+        <v>204</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Expected 404 after soft delete</t>
-        </is>
-      </c>
+      <c r="G26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1258,21 +1254,21 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Create user with invalid email</t>
+          <t>Get after delete</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -1281,7 +1277,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Expected 400 validation error</t>
+          <t>Expected 404 for deleted resource</t>
         </is>
       </c>
     </row>
@@ -1296,16 +1292,16 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/bookings</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Member books space with no plan (full hourly rate)</t>
+          <t>Invalid email</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>201</v>
+        <v>400</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>costCharged = hours x hourlyRate verified</t>
+          <t>Expected 400 validation failure</t>
         </is>
       </c>
     </row>
@@ -1334,22 +1330,18 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>endTime before startTime</t>
+          <t>Member books space (full hourly rate)</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>409</v>
+        <v>201</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Expected 4xx rejection (business rule)</t>
-        </is>
-      </c>
+      <c r="G29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1367,11 +1359,11 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Member-supplied foreign userId ignored, forced to own id</t>
+          <t>endTime before startTime</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>201</v>
+        <v>409</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
@@ -1380,7 +1372,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Response userId matches authenticated member</t>
+          <t>Expected 4xx business rule rejection</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Overlapping booking on same space/time</t>
+          <t>Member supplies foreign userId (ignored)</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
@@ -1411,11 +1403,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Auto-created as WAITLISTED + Waitlist row</t>
-        </is>
-      </c>
+      <c r="G31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1428,27 +1416,23 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/bookings/{id}/cancel</t>
+          <t>/api/v1/bookings</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Free cancellation (&gt;2h before start)</t>
+          <t>Overlapping booking -&gt; auto-WAITLISTED</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Credit hours refunded, costCharged=0 verified</t>
-        </is>
-      </c>
+      <c r="G32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1456,17 +1440,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>waitlist promotion</t>
+          <t>/api/v1/bookings/{id}/cancel</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Auto-promotion of earliest waitlisted booking on cancellation</t>
+          <t>Free cancellation (&gt;2h before start)</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
@@ -1477,11 +1461,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Booking transitioned WAITLISTED -&gt; CONFIRMED</t>
-        </is>
-      </c>
+      <c r="G33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1557,7 +1537,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Filter bookings by status</t>
+          <t>Filter by status</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
@@ -1615,7 +1595,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Overage billing beyond credit hours</t>
+          <t>Overage billing (credit hours exhausted)</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
@@ -1626,11 +1606,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>costCharged=25.00, creditHoursUsed=10.0 verified</t>
-        </is>
-      </c>
+      <c r="G38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1648,7 +1624,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Late cancellation (&lt;2h before start), 25% fee</t>
+          <t>Late cancellation (&lt;2h before start) -&gt; 25% fee</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
@@ -1659,11 +1635,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>costCharged = 9.17 x 0.25 = 2.29 verified</t>
-        </is>
-      </c>
+      <c r="G39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1692,11 +1664,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>totalAmount/overage aggregation verified</t>
-        </is>
-      </c>
+      <c r="G40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1727,7 +1695,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Expected 403 rejection (RBAC)</t>
+          <t>Expected 403 rejection</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1773,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Weekly space utilization % (Admin)</t>
+          <t>Weekly utilization % per space, includes averageRating (Admin)</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
@@ -1829,12 +1797,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/reports/revenue</t>
+          <t>/api/v1/reports/revenue?month=YYYY-MM</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Monthly revenue report (Admin)</t>
+          <t>Monthly revenue (Admin)</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
@@ -1858,12 +1826,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/reports/top-members</t>
+          <t>/api/v1/reports/top-members?limit=5</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Top 5 active members (Admin)</t>
+          <t>Top active members (Admin)</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
@@ -1905,7 +1873,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Expected 403 rejection (RBAC)</t>
+          <t>Expected 403 rejection</t>
         </is>
       </c>
     </row>
@@ -1920,16 +1888,16 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/bookings</t>
+          <t>/docs</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Reuse revoked API key</t>
+          <t>Swagger UI</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
@@ -1938,7 +1906,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Expected 401/403 rejection</t>
+          <t>302 redirect to /swagger-ui/index.html then 200</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1921,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>/docs</t>
+          <t>/api-docs</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Swagger UI</t>
+          <t>OpenAPI JSON includes new /api/v1/reviews paths</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
@@ -1969,11 +1937,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>302 redirect to /swagger-ui/index.html followed</t>
-        </is>
-      </c>
+      <c r="G49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -1986,12 +1950,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>/api-docs</t>
+          <t>/actuator/health</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI JSON</t>
+          <t>Health check</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
@@ -2015,12 +1979,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>/actuator/health</t>
+          <t>/api/v1/spaces</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Health check</t>
+          <t>List spaces includes averageRating/totalReviews</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
@@ -2032,6 +1996,601 @@
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/spaces/{id}</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Get single space includes averageRating/totalReviews</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reports/space-utilization</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Includes averageRating per space (Admin)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Create review, own COMPLETED booking, no existing review</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate review on same booking</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Expected 409, business rule 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Rating out of range (7)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Expected 400 validation failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Rating out of range (0)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Expected 400 validation failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Comment exceeds 500 characters</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Expected 400 validation failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Booking not COMPLETED</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Expected 400, business rule 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Someone else's booking</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Expected 403 ownership rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews?spaceId={id}</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>List reviews for a space, paginated, createdAt desc</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Get single review</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Edit own review (Member)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Edit another member's review</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Expected 403 ownership rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Delete another member's review</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>403</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Expected 403 ownership rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Delete own review (Member, soft delete)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Get soft-deleted review</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Expected 404, soft-deleted</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Admin deletes another user's review</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Business rule 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews?spaceId={id}</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>No API key</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Expected 401 rejection of unauthenticated request</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>/api-docs</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI JSON includes /api/v1/reviews paths</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
